--- a/product-import-template.xlsx
+++ b/product-import-template.xlsx
@@ -578,7 +578,7 @@
       <sqref>F2:F500</sqref>
     </dataValidation>
     <dataValidation type="list" allowBlank="1">
-      <formula1>Lists!$C$2:$C$60</formula1>
+      <formula1>Lists!$C$2:$C$61</formula1>
       <sqref>H2:H500</sqref>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0">
@@ -594,7 +594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -680,7 +680,7 @@
         <v>men-clothings</v>
       </c>
       <c r="C6" t="str">
-        <v>Anks</v>
+        <v>AnK's</v>
       </c>
       <c r="D6" t="str">
         <v>Green</v>
@@ -694,7 +694,7 @@
         <v>mens-clothings</v>
       </c>
       <c r="C7" t="str">
-        <v>BlazeMode</v>
+        <v>Anks</v>
       </c>
       <c r="D7" t="str">
         <v>Yellow</v>
@@ -702,13 +702,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>T-shirts</v>
+        <v>T-Shirts</v>
       </c>
       <c r="B8" t="str">
         <v>t-shirts</v>
       </c>
       <c r="C8" t="str">
-        <v>BuckleUp</v>
+        <v>BlazeMode</v>
       </c>
       <c r="D8" t="str">
         <v>Pink</v>
@@ -722,7 +722,7 @@
         <v>wearables</v>
       </c>
       <c r="C9" t="str">
-        <v>CapForce</v>
+        <v>BuckleUp</v>
       </c>
       <c r="D9" t="str">
         <v>Navy</v>
@@ -736,7 +736,7 @@
         <v>womens-clothing</v>
       </c>
       <c r="C10" t="str">
-        <v>ChicWear</v>
+        <v>CapForce</v>
       </c>
       <c r="D10" t="str">
         <v>Grey</v>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>ComfortWear</v>
+        <v>ChicWear</v>
       </c>
       <c r="D11" t="str">
         <v>Brown</v>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>ComfyChic</v>
+        <v>ComfortWear</v>
       </c>
       <c r="D12" t="str">
         <v>Beige</v>
@@ -778,7 +778,7 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>CoolKids</v>
+        <v>ComfyChic</v>
       </c>
       <c r="D13" t="str">
         <v>Maroon</v>
@@ -792,7 +792,7 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>CozyKnit</v>
+        <v>CoolKids</v>
       </c>
       <c r="D14" t="str">
         <v>Purple</v>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>CozyWear</v>
+        <v>CozyKnit</v>
       </c>
       <c r="D15" t="str">
         <v>Orange</v>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>DenimEdge</v>
+        <v>CozyWear</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -834,7 +834,7 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>DenimPro</v>
+        <v>DenimEdge</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -848,7 +848,7 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>DenimStyle</v>
+        <v>DenimPro</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -862,7 +862,7 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Elegance</v>
+        <v>DenimStyle</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -876,7 +876,7 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>EleganceWear</v>
+        <v>Elegance</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -890,7 +890,7 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>ExecutiveLine</v>
+        <v>EleganceWear</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -904,7 +904,7 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>FashionFlair</v>
+        <v>ExecutiveLine</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -918,7 +918,7 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>FitTime</v>
+        <v>FashionFlair</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -932,7 +932,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>FitTrack</v>
+        <v>FitTime</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>FlexFit</v>
+        <v>FitTrack</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -960,7 +960,7 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>GlamourStep</v>
+        <v>FlexFit</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -974,7 +974,7 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>GraceStep</v>
+        <v>GlamourStep</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>HealthSync</v>
+        <v>GraceStep</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1002,7 +1002,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>KidCap</v>
+        <v>HealthSync</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>KiddoWear</v>
+        <v>KidCap</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1030,7 +1030,7 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>LeatherCraft</v>
+        <v>KiddoWear</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1044,7 +1044,7 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>LittleTrendz</v>
+        <v>LeatherCraft</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1058,7 +1058,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>MiniDenim</v>
+        <v>LittleTrendz</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1072,7 +1072,7 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>PartyKids</v>
+        <v>MiniDenim</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -1086,7 +1086,7 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>PlayStep</v>
+        <v>PartyKids</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1100,7 +1100,7 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>PoloPro</v>
+        <v>PlayStep</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>PrincessWear</v>
+        <v>PoloPro</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -1128,7 +1128,7 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>PureCotton</v>
+        <v>PrincessWear</v>
       </c>
       <c r="D38" t="str">
         <v/>
@@ -1142,7 +1142,7 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>RainyDay</v>
+        <v>PureCotton</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -1156,7 +1156,7 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>RunFast</v>
+        <v>RainyDay</v>
       </c>
       <c r="D40" t="str">
         <v/>
@@ -1170,7 +1170,7 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>RunPro</v>
+        <v>RunFast</v>
       </c>
       <c r="D41" t="str">
         <v/>
@@ -1184,7 +1184,7 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>SharpDresser</v>
+        <v>RunPro</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -1198,7 +1198,7 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>SoundFit</v>
+        <v>SharpDresser</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>SportLine</v>
+        <v>SoundFit</v>
       </c>
       <c r="D44" t="str">
         <v/>
@@ -1226,7 +1226,7 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>StepChic</v>
+        <v>SportLine</v>
       </c>
       <c r="D45" t="str">
         <v/>
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>StepKids</v>
+        <v>StepChic</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -1254,7 +1254,7 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>StepUp</v>
+        <v>StepKids</v>
       </c>
       <c r="D47" t="str">
         <v/>
@@ -1268,7 +1268,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>StormGuard</v>
+        <v>StepUp</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -1282,7 +1282,7 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>SummerVibe</v>
+        <v>StormGuard</v>
       </c>
       <c r="D49" t="str">
         <v/>
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>TechTime</v>
+        <v>SummerVibe</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -1310,7 +1310,7 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Timeless</v>
+        <v>TechTime</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -1324,7 +1324,7 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>TinyFeet</v>
+        <v>Timeless</v>
       </c>
       <c r="D52" t="str">
         <v/>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>TrackMaster</v>
+        <v>TinyFeet</v>
       </c>
       <c r="D53" t="str">
         <v/>
@@ -1352,7 +1352,7 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>TrendStep</v>
+        <v>TrackMaster</v>
       </c>
       <c r="D54" t="str">
         <v/>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>UrbanChic</v>
+        <v>TrendStep</v>
       </c>
       <c r="D55" t="str">
         <v/>
@@ -1380,7 +1380,7 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>UrbanMan</v>
+        <v>UrbanChic</v>
       </c>
       <c r="D56" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>UrbanStyle</v>
+        <v>UrbanMan</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>VisionFit</v>
+        <v>UrbanStyle</v>
       </c>
       <c r="D58" t="str">
         <v/>
@@ -1422,7 +1422,7 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>WarmTouch</v>
+        <v>VisionFit</v>
       </c>
       <c r="D59" t="str">
         <v/>
@@ -1436,15 +1436,29 @@
         <v/>
       </c>
       <c r="C60" t="str">
+        <v>WarmTouch</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
         <v>ZenFit</v>
       </c>
-      <c r="D60" t="str">
+      <c r="D61" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1693,17 +1707,17 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>- At least ONE image source per row (image_files and/or image_urls). Rows with none get skipped with a reason.</v>
+        <v>- Images are OPTIONAL in this sheet — each row can get them from image_files, image_urls, OR a ZIP folder named exactly like the product (slugified folder names also match).</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>- ZIP must be a single .zip under 10 MB. jpg, jpeg, png, webp, gif, avif accepted. Files in subfolders are found by name.</v>
+        <v>- Rows that end up with zero loadable images are skipped with a clear reason — the rest still import.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>- No ZIP and no URLs? Use the folder trick: a zip folder named exactly like the product auto-matches all images inside it.</v>
+        <v>- ZIP must be a single .zip under 10 MB. jpg, jpeg, png, webp, gif, avif accepted. Files in subfolders are found by name.</v>
       </c>
     </row>
     <row r="30">
